--- a/data/result_20260903_110042 (linkage info).xlsx
+++ b/data/result_20260903_110042 (linkage info).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD22A26D-1ADC-4710-BCF2-8D3F16E18EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235BD2DA-AAFB-43A7-A9E6-897FEC13E7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results export'!$A$1:$J$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="21">
   <si>
     <t>target_user_id</t>
   </si>
@@ -100,6 +100,9 @@
   <si>
     <t>Fully Banned</t>
   </si>
+  <si>
+    <t>unique_target_user_id</t>
+  </si>
 </sst>
 </file>
 
@@ -156,9 +159,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2710,467 +2712,713 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A7D424-B2E7-4B94-B497-03DD547CEA0C}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>23938356</v>
+      </c>
+      <c r="B2">
         <v>2725817</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="e">
-        <f>_xlfn.XLOOKUP(A2,$F$2:$F$17,$F$2:$F$17)</f>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="e">
+        <f>_xlfn.XLOOKUP(B2,$G$2:$G$17,$G$2:$G$17)</f>
         <v>#N/A</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>13373294</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>23938356</v>
+      </c>
+      <c r="K2">
+        <v>2725817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
+        <v>23938356</v>
+      </c>
+      <c r="B3">
         <v>3560834</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="e">
-        <f t="shared" ref="D3:D27" si="0">_xlfn.XLOOKUP(A3,$F$2:$F$17,$F$2:$F$17)</f>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="e">
+        <f t="shared" ref="E3:E27" si="0">_xlfn.XLOOKUP(B3,$G$2:$G$17,$G$2:$G$17)</f>
         <v>#N/A</v>
       </c>
-      <c r="F3" s="1">
-        <v>23938356</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>23938356</v>
+      </c>
+      <c r="J3">
+        <v>23938356</v>
+      </c>
+      <c r="K3">
+        <v>3560834</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
+        <v>23938356</v>
+      </c>
+      <c r="B4">
         <v>3728701</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="e">
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4">
         <v>42459206</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>23938356</v>
+      </c>
+      <c r="K4">
+        <v>3728701</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
+        <v>23938356</v>
+      </c>
+      <c r="B5">
         <v>35433398</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="e">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F5">
-        <v>42598944</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>42598944</v>
+      </c>
+      <c r="J5">
+        <v>23938356</v>
+      </c>
+      <c r="K5">
+        <v>35433398</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
+        <v>42459206</v>
+      </c>
+      <c r="B6">
         <v>42458992</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="e">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6">
         <v>42758642</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>42459206</v>
+      </c>
+      <c r="K6">
+        <v>42458992</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
+        <v>42459206</v>
+      </c>
+      <c r="B7">
         <v>42459099</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
       <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="e">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>42787717</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>42459206</v>
+      </c>
+      <c r="K7">
+        <v>42459099</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
+        <v>42459206</v>
+      </c>
+      <c r="B8">
         <v>42459241</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="e">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8">
         <v>42814075</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>42459206</v>
+      </c>
+      <c r="K8">
+        <v>42459241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
+        <v>42459206</v>
+      </c>
+      <c r="B9">
         <v>42459298</v>
       </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
       <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="e">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9">
         <v>43376946</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>42459206</v>
+      </c>
+      <c r="K9">
+        <v>42459298</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
+        <v>42598944</v>
+      </c>
+      <c r="B10">
         <v>42011766</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
       <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="e">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10">
         <v>43485077</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>42598944</v>
+      </c>
+      <c r="K10">
+        <v>42011766</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
+        <v>42598944</v>
+      </c>
+      <c r="B11">
         <v>42406507</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
       <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="e">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11">
         <v>43512432</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>42598944</v>
+      </c>
+      <c r="K11">
+        <v>42406507</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
+        <v>42598944</v>
+      </c>
+      <c r="B12">
         <v>42426592</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
       <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="e">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12">
         <v>43701630</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>42598944</v>
+      </c>
+      <c r="K12">
+        <v>42426592</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
+        <v>42598944</v>
+      </c>
+      <c r="B13">
         <v>42426641</v>
       </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
       <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" t="e">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13">
         <v>43729827</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>42598944</v>
+      </c>
+      <c r="K13">
+        <v>42426641</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
+        <v>42598944</v>
+      </c>
+      <c r="B14">
         <v>42787717</v>
       </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
       <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14">
         <f t="shared" si="0"/>
         <v>42787717</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14">
         <v>43740668</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>42598944</v>
+      </c>
+      <c r="K14">
+        <v>42787717</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
+        <v>42598944</v>
+      </c>
+      <c r="B15">
         <v>43110281</v>
       </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
       <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="e">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15">
         <v>43756635</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>42598944</v>
+      </c>
+      <c r="K15">
+        <v>43110281</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
+        <v>42758642</v>
+      </c>
+      <c r="B16">
         <v>42705635</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
       <c r="C16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" t="e">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16">
         <v>43783789</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>42758642</v>
+      </c>
+      <c r="K16">
+        <v>42705635</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
+        <v>42758642</v>
+      </c>
+      <c r="B17">
         <v>42731028</v>
       </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
       <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" t="e">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17">
         <v>43811059</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>42758642</v>
+      </c>
+      <c r="K17">
+        <v>42731028</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
+        <v>23938356</v>
+      </c>
+      <c r="B18">
         <v>2380983</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="e">
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>23938356</v>
+      </c>
+      <c r="K18">
+        <v>2380983</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
+        <v>23938356</v>
+      </c>
+      <c r="B19">
         <v>2890343</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="e">
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>23938356</v>
+      </c>
+      <c r="K19">
+        <v>2890343</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
+        <v>23938356</v>
+      </c>
+      <c r="B20">
         <v>3149860</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" t="e">
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>23938356</v>
+      </c>
+      <c r="K20">
+        <v>3149860</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
+        <v>23938356</v>
+      </c>
+      <c r="B21">
         <v>3281435</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="e">
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>23938356</v>
+      </c>
+      <c r="K21">
+        <v>3281435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
+        <v>23938356</v>
+      </c>
+      <c r="B22">
         <v>26485962</v>
       </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
       <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" t="e">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>23938356</v>
+      </c>
+      <c r="K22">
+        <v>26485962</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
+        <v>42459206</v>
+      </c>
+      <c r="B23">
         <v>42459041</v>
       </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
       <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" t="e">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>42459206</v>
+      </c>
+      <c r="K23">
+        <v>42459041</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
+        <v>42459206</v>
+      </c>
+      <c r="B24">
         <v>42459148</v>
       </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
       <c r="C24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" t="e">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>42459206</v>
+      </c>
+      <c r="K24">
+        <v>42459148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
+        <v>42598944</v>
+      </c>
+      <c r="B25">
         <v>42758642</v>
       </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
       <c r="C25" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25">
         <f t="shared" si="0"/>
         <v>42758642</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>42598944</v>
+      </c>
+      <c r="K25">
+        <v>42758642</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
+        <v>42598944</v>
+      </c>
+      <c r="B26">
         <v>42814075</v>
       </c>
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
       <c r="C26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26">
         <f t="shared" si="0"/>
         <v>42814075</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>42598944</v>
+      </c>
+      <c r="K26">
+        <v>42814075</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>42598944</v>
-      </c>
-      <c r="B27" t="s">
-        <v>14</v>
+        <v>42758642</v>
+      </c>
+      <c r="B27">
+        <v>42598944</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27">
         <f t="shared" si="0"/>
+        <v>42598944</v>
+      </c>
+      <c r="J27">
+        <v>42758642</v>
+      </c>
+      <c r="K27">
         <v>42598944</v>
       </c>
     </row>
@@ -3181,266 +3429,375 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016BDD55-BEB4-46A1-BB59-4A1113469436}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>23938356</v>
+      </c>
+      <c r="B2" s="1">
         <v>2725817</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>23938356</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>23938356</v>
+      </c>
+      <c r="B3" s="1">
         <v>3560834</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>42459206</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>23938356</v>
+      </c>
+      <c r="B4" s="1">
         <v>3728701</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>42598944</v>
+      </c>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>23938356</v>
+      </c>
+      <c r="B5" s="1">
         <v>35433398</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>42758642</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>42459206</v>
+      </c>
+      <c r="B6" s="1">
         <v>42458992</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>42459206</v>
+      </c>
+      <c r="B7" s="1">
         <v>42459099</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>42459206</v>
+      </c>
+      <c r="B8" s="1">
         <v>42459241</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>42459206</v>
+      </c>
+      <c r="B9" s="1">
         <v>42459298</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>42598944</v>
+      </c>
+      <c r="B10" s="1">
         <v>42011766</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>42598944</v>
+      </c>
+      <c r="B11" s="1">
         <v>42406507</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>42598944</v>
+      </c>
+      <c r="B12" s="1">
         <v>42426592</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>42598944</v>
+      </c>
+      <c r="B13" s="1">
         <v>42426641</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>42598944</v>
+      </c>
+      <c r="B14" s="1">
         <v>43110281</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>42758642</v>
+      </c>
+      <c r="B15" s="1">
         <v>42705635</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>42758642</v>
+      </c>
+      <c r="B16" s="1">
         <v>42731028</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>23938356</v>
+      </c>
+      <c r="B17" s="1">
         <v>2380983</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>23938356</v>
+      </c>
+      <c r="B18" s="1">
         <v>2890343</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>23938356</v>
+      </c>
+      <c r="B19" s="1">
         <v>3149860</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="D19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>23938356</v>
+      </c>
+      <c r="B20" s="1">
         <v>3281435</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>23938356</v>
+      </c>
+      <c r="B21" s="1">
         <v>26485962</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="C21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>42459206</v>
+      </c>
+      <c r="B22" s="1">
         <v>42459041</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>42459206</v>
+      </c>
+      <c r="B23" s="1">
         <v>42459148</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="I23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
